--- a/data/credit_bond_all_2026-10-12.xlsx
+++ b/data/credit_bond_all_2026-10-12.xlsx
@@ -13860,7 +13860,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26闽西兴杭MTN004</t>
+          <t>26中关租赁SCP002</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13870,64 +13870,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>102683900.IB</t>
+          <t>012690004.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.40 ~ 1.63</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>41.26</v>
+        <v>31.46</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26闽西兴杭MTN003</t>
+          <t>24中关租赁MTN001</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>1.03Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.7096</t>
+          <t>1.6498</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>闽西兴杭国有资产投资经营有限公司</t>
+          <t>中关村科技租赁股份有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 24.03</t>
+          <t>D 4.89</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13937,12 +13937,12 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>10-12 10:00</t>
+          <t>10-12 09:00</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
@@ -13951,46 +13951,44 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.67%~1.71%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>福建省-龙岩市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>发行人募集资金1亿元,扣除承销费后全部用于归还发行人子公司有息债务</t>
+          <t>发行人本期超短期融资券发行规模4亿元,募集资金拟用于偿还债务融资工具。[26中关租赁SCP001]</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>北京银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
@@ -14005,7 +14003,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>闽西兴杭国有资产投资经营有限公司2026年度第四期中期票据</t>
+          <t>中关村科技租赁股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -14015,14 +14013,10 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK59" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-07-09</t>
+        </is>
+      </c>
+      <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -14030,7 +14024,7 @@
       </c>
       <c r="AM59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AN59" s="3" t="inlineStr">
@@ -14040,32 +14034,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -14094,13 +14088,13 @@
         </is>
       </c>
       <c r="AZ59" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26新海连MTN005</t>
+          <t>26闽西兴杭MTN004</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -14110,64 +14104,64 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>102690059.IB</t>
+          <t>102683900.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>40.76</v>
+        <v>41.26</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26新海连MTN002</t>
+          <t>26闽西兴杭MTN003</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>4.74Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.8061</t>
+          <t>1.7096</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>江苏新海连发展集团有限公司</t>
+          <t>闽西兴杭国有资产投资经营有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 11.50</t>
+          <t>C- 24.03</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14177,12 +14171,12 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>10-12 13:00</t>
+          <t>10-12 10:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
@@ -14191,38 +14185,40 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="V60" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>福建省-龙岩市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行不超过4.00亿元中期票据,用于偿还发行人存量债务融资工具的本金[23新海连MTN004]</t>
+          <t>发行人募集资金1亿元,扣除承销费后全部用于归还发行人子公司有息债务</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,招商证券股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
@@ -14243,7 +14239,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>江苏新海连发展集团有限公司2026年度第五期中期票据</t>
+          <t>闽西兴杭国有资产投资经营有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14253,10 +14249,14 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK60" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK60" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL60" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
@@ -14284,22 +14284,22 @@
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>黄金</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14327,64 +14327,66 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ60" s="3"/>
+      <c r="AZ60" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26乌开01</t>
+          <t>26新海连MTN005</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>10-12 19:00</t>
+          <t>10-12 18:00</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>284158.SH</t>
+          <t>102690059.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>74.35</v>
+        <v>40.76</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>24乌开06</t>
+          <t>26新海连MTN002</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>3.21Y</t>
+          <t>4.74Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.7405</t>
+          <t>1.8061</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -14394,12 +14396,12 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>乌鲁木齐经济技术开发区建设投资开发(集团)有限公司</t>
+          <t>江苏新海连发展集团有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C- 13.65</t>
+          <t>C- 11.50</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14409,7 +14411,7 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>10-12 15:00</t>
+          <t>10-12 13:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -14423,17 +14425,17 @@
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>3.98</v>
+        <v>4.0</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>2.16%~2.26%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
@@ -14444,23 +14446,23 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,用于偿还到期公司债本金[23乌开01]</t>
+          <t>发行人本期拟发行不超过4.00亿元中期票据,用于偿还发行人存量债务融资工具的本金[23新海连MTN004]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,太平洋证券股份有限公司,国开证券股份有限公司</t>
+          <t>东吴证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
@@ -14470,28 +14472,28 @@
       </c>
       <c r="AG61" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>乌鲁木齐经济技术开发区建设投资开发(集团)有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏新海连发展集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2033-10-13</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AM61" s="3" t="inlineStr">
@@ -14511,7 +14513,7 @@
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
@@ -14564,70 +14566,74 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26芜湖投控MTN002</t>
+          <t>26乌开01</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>10-12 18:00</t>
+          <t>10-12 19:00</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>102683942.IB</t>
+          <t>284158.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>8.62</v>
+        <v>5.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>8.62</v>
+        <v>5.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>74.35</v>
+      </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26芜湖投控MTN001</t>
+          <t>24乌开06</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>3.21Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.7706</t>
+          <t>1.7405</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>1.7900/1.7200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>芜湖市投资控股集团有限公司</t>
+          <t>乌鲁木齐经济技术开发区建设投资开发(集团)有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 15.59</t>
+          <t>C- 13.65</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14637,60 +14643,58 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>10-12 09:00</t>
+          <t>10-12 15:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>4.92</v>
-      </c>
+        <v>3.98</v>
+      </c>
+      <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.16%~2.26%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为8.62亿元,所募集资金用于偿还债务融资工具本金。[23芜湖建设MTN005]</t>
+          <t>本期债券募集资金扣除发行费用后,用于偿还到期公司债本金[23乌开01]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,徽商银行股份有限公司</t>
+          <t>平安证券股份有限公司,太平洋证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
@@ -14700,38 +14704,38 @@
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>芜湖市投资控股集团有限公司2026年度第二期中期票据</t>
+          <t>乌鲁木齐经济技术开发区建设投资开发(集团)有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2031-10-15</t>
+          <t>2033-10-13</t>
         </is>
       </c>
       <c r="AK62" s="3"/>
       <c r="AL62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AO62" s="3" t="inlineStr">
@@ -14741,27 +14745,27 @@
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>汽车零部件</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14789,14 +14793,12 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ62" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ62" s="3"/>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26苏州资产MTN004</t>
+          <t>26芜湖投控MTN002</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14806,64 +14808,60 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>102683927.IB</t>
+          <t>102683942.IB</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4.0</v>
+        <v>8.62</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>4.0</v>
+        <v>8.62</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>25.26</v>
-      </c>
+          <t>1.40 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>24苏资G2</t>
+          <t>26芜湖投控MTN001</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.6758</t>
+          <t>1.7706</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/1.7200</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>苏州资产管理有限公司</t>
+          <t>芜湖市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C- 13.65</t>
+          <t>C- 15.59</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14878,28 +14876,28 @@
       </c>
       <c r="S63" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>3.875</v>
+        <v>7.05</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>1.33</v>
+        <v>4.92</v>
       </c>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -14910,17 +14908,17 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具拟发行4亿元，募集资金用于偿还有息负债[25苏州资产MTN005]</t>
+          <t>本期发行金额为8.62亿元,所募集资金用于偿还债务融资工具本金。[23芜湖建设MTN005]</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
@@ -14941,7 +14939,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>苏州资产管理有限公司2026年度第四期中期票据</t>
+          <t>芜湖市投资控股集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14951,17 +14949,13 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK63" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-15</t>
+        </is>
+      </c>
+      <c r="AK63" s="3"/>
       <c r="AL63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AM63" s="3" t="inlineStr">
@@ -14971,12 +14965,12 @@
       </c>
       <c r="AN63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP63" s="3" t="inlineStr">
@@ -14986,22 +14980,22 @@
       </c>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>汽车零部件</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
@@ -15029,12 +15023,14 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ63" s="3"/>
+      <c r="AZ63" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26昌平科技SCP003</t>
+          <t>26苏州资产MTN004</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -15044,64 +15040,64 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>012682395.IB</t>
+          <t>102683927.IB</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.65</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>39.46</v>
+        <v>25.26</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26昌平科技SCP002</t>
+          <t>24苏资G2</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>45D</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.4700</t>
+          <t>1.6758</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>--/1.4500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>北京昌平科技园发展集团有限公司</t>
+          <t>苏州资产管理有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C 27.52</t>
+          <t>C- 13.65</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -15116,7 +15112,7 @@
       </c>
       <c r="S64" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T64" s="3" t="inlineStr">
@@ -15125,46 +15121,46 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>1.8</v>
+        <v>3.875</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>4.33</v>
+        <v>1.33</v>
       </c>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>北京市-昌平区</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为3亿元,用于偿还发行人有息负债[26昌平科技SCP001]</t>
+          <t>本期债务融资工具拟发行4亿元，募集资金用于偿还有息负债[25苏州资产MTN005]</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>苏州银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
       <c r="AE64" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF64" s="3" t="inlineStr">
@@ -15179,7 +15175,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>北京昌平科技园发展集团有限公司2026年度第三期超短期融资券</t>
+          <t>苏州资产管理有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15189,7 +15185,7 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2027-07-10</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK64" s="3" t="inlineStr">
@@ -15214,32 +15210,32 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15272,7 +15268,7 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26盛裕投资PPN002</t>
+          <t>26昌平科技SCP003</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -15282,64 +15278,64 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>032690037.IB</t>
+          <t>012682395.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2.5</v>
+        <v>3.0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2.5</v>
+        <v>3.0</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.35 ~ 1.65</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>58.76</v>
+        <v>39.46</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>24盛裕投资PPN002</t>
+          <t>26昌平科技SCP002</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>45D</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1.8261</t>
+          <t>1.4700</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>--/1.4500</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>扬州盛裕投资发展有限公司</t>
+          <t>北京昌平科技园发展集团有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>C 27.00</t>
+          <t>C 27.52</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15354,7 +15350,7 @@
       </c>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr">
@@ -15363,19 +15359,19 @@
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>8.0</v>
+        <v>4.33</v>
       </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -15386,23 +15382,23 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>北京市-昌平区</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具注册金额2.50亿元，本期发行金额2.50亿元，根据发行人的财务状况和资金需求情况，募集资金拟用于偿还发行人存量债务融资工具本金[23 盛裕投资PPN001]</t>
+          <t>本期超短期融资券发行金额为3亿元,用于偿还发行人有息负债[26昌平科技SCP001]</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -15417,20 +15413,24 @@
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>扬州盛裕投资发展有限公司2026年度第二期定向债务融资工具</t>
+          <t>北京昌平科技园发展集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
-        </is>
-      </c>
-      <c r="AK65" s="3"/>
+          <t>2027-07-10</t>
+        </is>
+      </c>
+      <c r="AK65" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL65" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -15448,32 +15448,32 @@
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -15501,75 +15501,79 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ65" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ65" s="3"/>
     </row>
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26南康05(取消发行)</t>
+          <t>26盛裕投资PPN002</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>10-12 19:00</t>
+          <t>10-12 18:00</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>DY284138.SH</t>
+          <t>032690037.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>58.76</v>
+      </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>26南康02</t>
+          <t>24盛裕投资PPN002</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>4.33Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>2.0167</t>
+          <t>1.8261</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>2.0500/1.9500</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>赣州市南康区城市建设发展集团有限公司</t>
+          <t>扬州盛裕投资发展有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C 28.70</t>
+          <t>C 27.00</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15579,12 +15583,12 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>10-12 15:00</t>
+          <t>10-12 09:00</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
@@ -15592,11 +15596,15 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
+      <c r="U66" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V66" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
@@ -15612,23 +15620,23 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>江西省-赣州市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过人民币8.00亿元(含人民币8.00亿元)。本期债券募集资金扣除发行费用后,拟用于偿还公司债券本金[23南康03]</t>
+          <t>本期定向债务融资工具注册金额2.50亿元，本期发行金额2.50亿元，根据发行人的财务状况和资金需求情况，募集资金拟用于偿还发行人存量债务融资工具本金[23 盛裕投资PPN001]</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>申港证券股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF66" s="3" t="inlineStr">
@@ -15638,12 +15646,12 @@
       </c>
       <c r="AG66" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>赣州市南康区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)(取消发行)</t>
+          <t>扬州盛裕投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -15653,90 +15661,88 @@
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK66" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK66" s="3"/>
       <c r="AL66" s="3" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ66" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM66" s="3" t="inlineStr">
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY66" s="3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO66" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP66" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ66" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR66" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS66" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT66" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU66" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV66" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW66" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX66" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY66" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AZ66" s="3"/>
+      <c r="AZ66" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26涪交02</t>
+          <t>26南康05(取消发行)</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15746,64 +15752,58 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>284111.SH</t>
+          <t>DY284138.SH</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>12.0</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>65.35</v>
-      </c>
+          <t>1.50 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>24涪陵交通PPN001</t>
+          <t>26南康02</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2.74Y</t>
+          <t>4.33Y</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.8228</t>
+          <t>2.0167</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0500/1.9500</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵交通旅游建设投资集团有限公司</t>
+          <t>赣州市南康区城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>D- 1.80</t>
+          <t>C 28.70</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>10-12 16:00</t>
+          <t>10-12 15:00</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -15826,18 +15826,16 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="U67" s="4" t="n">
-        <v>4.61</v>
-      </c>
+      <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
@@ -15848,17 +15846,17 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江西省-赣州市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还回售的公司债券本金。[23涪交01]</t>
+          <t>本期债券发行金额为不超过人民币8.00亿元(含人民币8.00亿元)。本期债券募集资金扣除发行费用后,拟用于偿还公司债券本金[23南康03]</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,西南证券股份有限公司,中邮证券有限责任公司,长城证券股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司</t>
+          <t>申港证券股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
@@ -15879,7 +15877,7 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵交通旅游建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>赣州市南康区城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15889,18 +15887,22 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2033-10-13</t>
-        </is>
-      </c>
-      <c r="AK67" s="3"/>
+          <t>2029-10-13</t>
+        </is>
+      </c>
+      <c r="AK67" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AN67" s="3" t="inlineStr">
@@ -15915,7 +15917,7 @@
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
@@ -15925,12 +15927,12 @@
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
@@ -15968,7 +15970,7 @@
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26涪交01</t>
+          <t>26涪交02</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15978,34 +15980,34 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>284110.SH</t>
+          <t>284111.SH</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
         <v>9.0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>52.76</v>
+        <v>65.35</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
@@ -16059,7 +16061,7 @@
         </is>
       </c>
       <c r="U68" s="4" t="n">
-        <v>6.15</v>
+        <v>4.61</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
@@ -16069,7 +16071,7 @@
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -16111,7 +16113,7 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵交通旅游建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>重庆市涪陵交通旅游建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
@@ -16121,7 +16123,7 @@
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2033-10-13</t>
         </is>
       </c>
       <c r="AK68" s="3"/>
@@ -16200,59 +16202,59 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26杭实投SCP010</t>
+          <t>26涪交01</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>10-12 18:00</t>
+          <t>10-12 19:00</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>012682398.IB</t>
+          <t>284110.SH</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>0.3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.60</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>1.32</v>
+        <v>1.93</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>14.95</v>
+        <v>52.76</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>23杭实K3</t>
+          <t>24涪陵交通PPN001</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>48D</t>
+          <t>2.74Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1.4286</t>
+          <t>1.8228</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -16262,12 +16264,12 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>杭州市实业投资集团有限公司</t>
+          <t>重庆市涪陵交通旅游建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>B- 42.17</t>
+          <t>D- 1.80</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16277,7 +16279,7 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>10-12 10:00</t>
+          <t>10-12 16:00</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -16291,46 +16293,44 @@
         </is>
       </c>
       <c r="U69" s="4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V69" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>6.15</v>
+      </c>
+      <c r="V69" s="3"/>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金10亿元,用于补充集团本部及下属子公司营运资金和偿还存量融资</t>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还回售的公司债券本金。[23涪交01]</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>申万宏源证券有限公司,西南证券股份有限公司,中邮证券有限责任公司,长城证券股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -16340,37 +16340,33 @@
       </c>
       <c r="AG69" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>杭州市实业投资集团有限公司2026年度第十期超短期融资券</t>
+          <t>重庆市涪陵交通旅游建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
-        </is>
-      </c>
-      <c r="AK69" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-10-13</t>
+        </is>
+      </c>
+      <c r="AK69" s="3"/>
       <c r="AL69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AM69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN69" s="3" t="inlineStr">
@@ -16380,32 +16376,32 @@
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>橡胶</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
@@ -16433,14 +16429,12 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ69" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ69" s="3"/>
     </row>
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26徐州产城MTN004</t>
+          <t>26杭实投SCP010</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -16450,100 +16444,100 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>102683933.IB</t>
+          <t>012682398.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>0.3Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>7.15</v>
+        <v>10.0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>7.15</v>
+        <v>10.0</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.26</t>
+          <t>1.20 ~ 1.60</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>23杭实K3</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>48D</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>1.4286</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>杭州市实业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>B- 42.17</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>10-12 10:00</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T70" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="U70" s="4" t="n">
         <v>2.22</v>
       </c>
-      <c r="I70" s="4" t="n">
-        <v>54.78</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>26徐州产城MTN003</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>9.85Y</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>2.2584</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="inlineStr">
-        <is>
-          <t>--/2.1800</t>
-        </is>
-      </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>徐州市产城发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>B- 35.59</t>
-        </is>
-      </c>
-      <c r="Q70" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="R70" s="3" t="inlineStr">
-        <is>
-          <t>10-12 09:00</t>
-        </is>
-      </c>
-      <c r="S70" s="3" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="T70" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="n">
-        <v>2.4755</v>
-      </c>
       <c r="V70" s="4" t="n">
-        <v>4.67</v>
+        <v>1.0</v>
       </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -16554,23 +16548,23 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额7.15亿元，募集资金拟全部用于偿还债务融资工具本金[23徐州产城MTN003]</t>
+          <t>本期超短期融资券募集资金10亿元,用于补充集团本部及下属子公司营运资金和偿还存量融资</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
@@ -16585,7 +16579,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>徐州市产城发展集团有限公司2026年度第四期中期票据</t>
+          <t>杭州市实业投资集团有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -16595,10 +16589,14 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2036-10-13</t>
-        </is>
-      </c>
-      <c r="AK70" s="3"/>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="AK70" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL70" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -16616,32 +16614,32 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>橡胶</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16676,7 +16674,7 @@
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26自贡城投MTN001</t>
+          <t>26徐州产城MTN004</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16686,64 +16684,64 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>102683901.IB</t>
+          <t>102683933.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>9.0</v>
+        <v>7.15</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>9.0</v>
+        <v>7.15</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.20</t>
+          <t>1.80 ~ 2.26</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>2.0</v>
+        <v>2.22</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>59.76</v>
+        <v>54.78</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>25自贡城投MTN002</t>
+          <t>26徐州产城MTN003</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>3.88Y</t>
+          <t>9.85Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.9001</t>
+          <t>2.2584</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>--/1.8500</t>
+          <t>--/2.1800</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>自贡市城市建设投资开发集团有限公司</t>
+          <t>徐州市产城发展集团有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>C 27.72</t>
+          <t>B- 35.59</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16758,7 +16756,7 @@
       </c>
       <c r="S71" s="3" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="T71" s="3" t="inlineStr">
@@ -16767,40 +16765,40 @@
         </is>
       </c>
       <c r="U71" s="4" t="n">
-        <v>6.4667</v>
+        <v>2.4755</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>3.67</v>
+        <v>4.67</v>
       </c>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>2.13%~2.23%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>四川省-自贡市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为9亿元，募集资金计划全部用于偿还发行人已发行的债务融资工具本金【23自贡城投PPN001】</t>
+          <t>本期中期票据发行金额7.15亿元，募集资金拟全部用于偿还债务融资工具本金[23徐州产城MTN003]</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,徽商银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
@@ -16821,7 +16819,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>自贡市城市建设投资开发集团有限公司2026年度第一期中期票据</t>
+          <t>徐州市产城发展集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16831,7 +16829,7 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2036-10-13</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
@@ -16842,7 +16840,7 @@
       </c>
       <c r="AM71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AN71" s="3" t="inlineStr">
@@ -16857,7 +16855,7 @@
       </c>
       <c r="AP71" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ71" s="3" t="inlineStr">
@@ -16906,13 +16904,13 @@
         </is>
       </c>
       <c r="AZ71" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26平安点创CP001</t>
+          <t>26自贡城投MTN001</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -16922,64 +16920,64 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>042680335.IB</t>
+          <t>102683901.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.71</t>
+          <t>2.00 ~ 3.20</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.67</v>
+        <v>2.0</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>46.53</v>
+        <v>59.76</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>25平安点创MTN003</t>
+          <t>25自贡城投MTN002</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>1.04Y</t>
+          <t>3.88Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.7112</t>
+          <t>1.9001</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>平安点创国际融资租赁有限公司</t>
+          <t>自贡市城市建设投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C- 17.53</t>
+          <t>C 27.72</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16994,7 +16992,7 @@
       </c>
       <c r="S72" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="T72" s="3" t="inlineStr">
@@ -17003,51 +17001,51 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>1.9</v>
+        <v>6.4667</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.75%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>四川省-自贡市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>发行人本期短期融资券基础发行规模为人民币0亿元，发行规模上限为人民币4亿元，拟用于偿还发行人即将到期的债务融资工具[26平安点创SCP001]</t>
+          <t>本次中期票据发行金额为9亿元，募集资金计划全部用于偿还发行人已发行的债务融资工具本金【23自贡城投PPN001】</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司,浙商银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
       <c r="AE72" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF72" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG72" s="3" t="inlineStr">
@@ -17057,7 +17055,7 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>平安点创国际融资租赁有限公司2026年度第一期短期融资券</t>
+          <t>自贡市城市建设投资开发集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -17067,7 +17065,7 @@
       </c>
       <c r="AJ72" s="3" t="inlineStr">
         <is>
-          <t>2027-10-13</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK72" s="3"/>
@@ -17078,7 +17076,7 @@
       </c>
       <c r="AM72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN72" s="3" t="inlineStr">
@@ -17088,32 +17086,32 @@
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU72" s="3" t="inlineStr">
@@ -17141,12 +17139,14 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ72" s="3"/>
+      <c r="AZ72" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26柳州东投MTN002</t>
+          <t>26平安点创CP001</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -17156,49 +17156,49 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>102683894.IB</t>
+          <t>042680335.IB</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3.07</v>
+        <v>4.0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>3.07</v>
+        <v>4.0</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.31 ~ 1.71</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>88.76</v>
+        <v>46.53</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>26柳州东投MTN001</t>
+          <t>25平安点创MTN003</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>4.88Y</t>
+          <t>1.04Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>2.2311</t>
+          <t>1.7112</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -17208,12 +17208,12 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>广西柳州市东城投资开发集团有限公司</t>
+          <t>平安点创国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.84</t>
+          <t>C- 17.53</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17223,12 +17223,12 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>10-12 14:00</t>
+          <t>10-12 09:00</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T73" s="3" t="inlineStr">
@@ -17237,49 +17237,51 @@
         </is>
       </c>
       <c r="U73" s="4" t="n">
-        <v>2.3453</v>
-      </c>
-      <c r="V73" s="3"/>
+        <v>1.9</v>
+      </c>
+      <c r="V73" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.71%~1.75%</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-柳州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>公司发行本期中期票据规模不超过3.07亿元，用于优化债务结构，所偿还债务均不属于政府隐性债务[ 23柳州东投MTN002， 21柳州东投PPN003]。</t>
+          <t>发行人本期短期融资券基础发行规模为人民币0亿元，发行规模上限为人民币4亿元，拟用于偿还发行人即将到期的债务融资工具[26平安点创SCP001]</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,长城证券股份有限公司</t>
+          <t>交通银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG73" s="3" t="inlineStr">
@@ -17289,7 +17291,7 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>广西柳州市东城投资开发集团有限公司2026年度第二期中期票据</t>
+          <t>平安点创国际融资租赁有限公司2026年度第一期短期融资券</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
@@ -17299,7 +17301,7 @@
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2027-10-13</t>
         </is>
       </c>
       <c r="AK73" s="3"/>
@@ -17310,7 +17312,7 @@
       </c>
       <c r="AM73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AN73" s="3" t="inlineStr">
@@ -17320,32 +17322,32 @@
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP73" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ73" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
@@ -17378,7 +17380,7 @@
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26天成租赁SCP028</t>
+          <t>26柳州东投MTN002</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -17388,49 +17390,49 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>012682407.IB</t>
+          <t>102683894.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>0.37Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>5.0</v>
+        <v>3.07</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>5.0</v>
+        <v>3.07</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.44</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1.44</v>
+        <v>2.29</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>25.34</v>
+        <v>88.76</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>GC天成06</t>
+          <t>26柳州东投MTN001</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>150D</t>
+          <t>4.88Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1.4545</t>
+          <t>2.2311</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -17440,12 +17442,12 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>华能天成融资租赁有限公司</t>
+          <t>广西柳州市东城投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.01</t>
+          <t>C+ 31.84</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17455,7 +17457,7 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>10-12 09:00</t>
+          <t>10-12 14:00</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -17469,49 +17471,49 @@
         </is>
       </c>
       <c r="U74" s="4" t="n">
-        <v>0.5</v>
+        <v>2.3453</v>
       </c>
       <c r="V74" s="3"/>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z74" s="3"/>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广西壮族自治区-柳州市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额5亿元。本期债务融资工具全部募集资金拟用于偿还到期的债务融资工具[26天成租赁SCP012(绿色)]</t>
+          <t>公司发行本期中期票据规模不超过3.07亿元，用于优化债务结构，所偿还债务均不属于政府隐性债务[ 23柳州东投MTN002， 21柳州东投PPN003]。</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司</t>
+          <t>东方证券股份有限公司,长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
       <c r="AE74" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF74" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG74" s="3" t="inlineStr">
@@ -17521,7 +17523,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>华能天成融资租赁有限公司2026年度第二十八期超短期融资券</t>
+          <t>广西柳州市东城投资开发集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17531,7 +17533,7 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK74" s="3"/>
@@ -17542,7 +17544,7 @@
       </c>
       <c r="AM74" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN74" s="3" t="inlineStr">
@@ -17552,32 +17554,32 @@
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP74" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ74" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU74" s="3" t="inlineStr">
@@ -17610,7 +17612,7 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26抚州投资MTN002</t>
+          <t>26天成租赁SCP028</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -17620,64 +17622,64 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>102683918.IB</t>
+          <t>012682407.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.37Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>11.6</v>
+        <v>5.0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>11.6</v>
+        <v>5.0</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>1.30 ~ 1.44</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>42.76</v>
+        <v>25.34</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26抚州03</t>
+          <t>GC天成06</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>150D</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.9260</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/1.8100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>抚州市市属国有资产投资控股集团有限公司</t>
+          <t>华能天成融资租赁有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>C 29.82</t>
+          <t>C+ 30.01</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17692,7 +17694,7 @@
       </c>
       <c r="S75" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T75" s="3" t="inlineStr">
@@ -17701,51 +17703,49 @@
         </is>
       </c>
       <c r="U75" s="4" t="n">
-        <v>4.1466</v>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>1.3</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>江西省-抚州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额11.6亿元,募集资金拟全部用于偿还发行人债务融资工具本金[23抚州投资MTN001,21抚州投资MTN003]</t>
+          <t>本期债务融资工具发行金额5亿元。本期债务融资工具全部募集资金拟用于偿还到期的债务融资工具[26天成租赁SCP012(绿色)]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,交通银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG75" s="3" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>抚州市市属国有资产投资控股集团有限公司2026年度第二期中期票据</t>
+          <t>华能天成融资租赁有限公司2026年度第二十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
@@ -17786,32 +17786,32 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17844,7 +17844,7 @@
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26武汉城建MTN004</t>
+          <t>26抚州投资MTN002</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>102683924.IB</t>
+          <t>102683918.IB</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -17863,55 +17863,55 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>16.0</v>
+        <v>11.6</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>16.0</v>
+        <v>11.6</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>34.76</v>
+        <v>42.76</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>26武汉城建MTN003</t>
+          <t>26抚州03</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>4.87Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1.7597</t>
+          <t>1.9260</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7200</t>
+          <t>--/1.8100</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>武汉城市建设集团有限公司</t>
+          <t>抚州市市属国有资产投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>B- 39.87</t>
+          <t>C 29.82</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="S76" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T76" s="3" t="inlineStr">
@@ -17935,44 +17935,40 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>5.2875</v>
+        <v>4.1466</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>3.07</v>
+        <v>1.3</v>
       </c>
       <c r="W76" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z76" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江西省-抚州市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模16亿元,募集资金计划用于偿还发行人本部债务融资工具本金[26武汉城建SCP001,26武汉城建SCP002]</t>
+          <t>本期中期票据发行金额11.6亿元,募集资金拟全部用于偿还发行人债务融资工具本金[23抚州投资MTN001,21抚州投资MTN003]</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司,恒丰银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
@@ -17993,7 +17989,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>武汉城市建设集团有限公司2026年度第四期中期票据</t>
+          <t>抚州市市属国有资产投资控股集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -18024,32 +18020,32 @@
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">
@@ -18077,14 +18073,12 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ76" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ76" s="3"/>
     </row>
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26澳柯玛集MTN001</t>
+          <t>26武汉城建MTN004</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -18094,7 +18088,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>102683920.IB</t>
+          <t>102683924.IB</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -18103,55 +18097,55 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H77" s="4" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>74.76</v>
+        <v>34.76</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>25澳柯玛集MTN001</t>
+          <t>26武汉城建MTN003</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>3.26Y</t>
+          <t>4.87Y</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>2.1188</t>
+          <t>1.7597</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>2.1100/--</t>
+          <t>1.7600/1.7200</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>青岛澳柯玛控股集团有限公司</t>
+          <t>武汉城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>B- 40.04</t>
+          <t>B- 39.87</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18166,7 +18160,7 @@
       </c>
       <c r="S77" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T77" s="3" t="inlineStr">
@@ -18175,24 +18169,24 @@
         </is>
       </c>
       <c r="U77" s="4" t="n">
-        <v>2.64</v>
+        <v>5.2875</v>
       </c>
       <c r="V77" s="4" t="n">
-        <v>1.12</v>
+        <v>3.07</v>
       </c>
       <c r="W77" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>2.01%~2.11%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z77" s="3" t="inlineStr">
@@ -18202,24 +18196,20 @@
       </c>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模5亿元,募集资金全部用于偿还发行人本部债务融资工具[26澳柯玛集SCP001,23澳柯玛集MTN001]</t>
+          <t>本期债务融资工具发行规模16亿元,募集资金计划用于偿还发行人本部债务融资工具本金[26武汉城建SCP001,26武汉城建SCP002]</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD77" s="3" t="inlineStr">
-        <is>
-          <t>青岛海发国有资本投资运营集团有限公司</t>
-        </is>
-      </c>
+          <t>交通银行股份有限公司,恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD77" s="3"/>
       <c r="AE77" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -18237,7 +18227,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>青岛澳柯玛控股集团有限公司2026年度第一期中期票据</t>
+          <t>武汉城市建设集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -18268,32 +18258,32 @@
       </c>
       <c r="AO77" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>家用电器</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
         <is>
-          <t>家用电器</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT77" s="3" t="inlineStr">
         <is>
-          <t>白色家电</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU77" s="3" t="inlineStr">
@@ -18303,7 +18293,7 @@
       </c>
       <c r="AV77" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW77" s="3" t="inlineStr">
@@ -18328,7 +18318,7 @@
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26武清经开MTN008</t>
+          <t>26澳柯玛集MTN001</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -18338,64 +18328,64 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>102683905.IB</t>
+          <t>102683920.IB</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>2.5Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1.4</v>
+        <v>5.0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1.4</v>
+        <v>5.0</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>59.77</v>
+        <v>74.76</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>26武清经开MTN003</t>
+          <t>25澳柯玛集MTN001</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2.41Y</t>
+          <t>3.26Y</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.8438</t>
+          <t>2.1188</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1100/--</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>天津武清经济技术开发区有限公司</t>
+          <t>青岛澳柯玛控股集团有限公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C 28.09</t>
+          <t>B- 40.04</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18410,7 +18400,7 @@
       </c>
       <c r="S78" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="T78" s="3" t="inlineStr">
@@ -18419,41 +18409,51 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>1.7714</v>
-      </c>
-      <c r="V78" s="3"/>
+        <v>2.64</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>1.12</v>
+      </c>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.01%~2.11%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z78" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z78" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>天津市-武清区</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债券基础发行规模0亿元，发行金额上限1.4亿元，用于偿还存量债务融资工具[25 武清经开MTN003]。</t>
+          <t>本期中期票据发行规模5亿元,募集资金全部用于偿还发行人本部债务融资工具[26澳柯玛集SCP001,23澳柯玛集MTN001]</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD78" s="3"/>
+          <t>北京银行股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD78" s="3" t="inlineStr">
+        <is>
+          <t>青岛海发国有资本投资运营集团有限公司</t>
+        </is>
+      </c>
       <c r="AE78" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>天津武清经济技术开发区有限公司2026年度第八期中期票据</t>
+          <t>青岛澳柯玛控股集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2029-04-12</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK78" s="3"/>
@@ -18492,7 +18492,7 @@
       </c>
       <c r="AM78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AN78" s="3" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="AO78" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP78" s="3" t="inlineStr">
@@ -18512,22 +18512,22 @@
       </c>
       <c r="AQ78" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子设备制造</t>
         </is>
       </c>
       <c r="AR78" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>家用电器</t>
         </is>
       </c>
       <c r="AS78" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>家用电器</t>
         </is>
       </c>
       <c r="AT78" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>白色家电</t>
         </is>
       </c>
       <c r="AU78" s="3" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AV78" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW78" s="3" t="inlineStr">
@@ -18555,12 +18555,14 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ78" s="3"/>
+      <c r="AZ78" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26绿城水务MTN004</t>
+          <t>26武清经开MTN008</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18570,64 +18572,64 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>102683910.IB</t>
+          <t>102683905.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2.5Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>3.0</v>
+        <v>1.4</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>3.0</v>
+        <v>1.4</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 1.92</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>39.76</v>
+        <v>59.77</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>26绿城水务MTN003</t>
+          <t>26武清经开MTN003</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.41Y</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>1.9125</t>
+          <t>1.8438</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>--/1.8500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>广西绿城水务集团股份有限公司</t>
+          <t>天津武清经济技术开发区有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C- 14.31</t>
+          <t>C 28.09</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18637,12 +18639,12 @@
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>10-12 15:00</t>
+          <t>10-12 09:00</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T79" s="3" t="inlineStr">
@@ -18651,17 +18653,17 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>4.65</v>
+        <v>1.7714</v>
       </c>
       <c r="V79" s="3"/>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -18672,17 +18674,17 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>天津市-武清区</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>发行人拟发行金额为3亿元,用于偿还发行人有息债务</t>
+          <t>发行人本期债券基础发行规模0亿元，发行金额上限1.4亿元，用于偿还存量债务融资工具[25 武清经开MTN003]。</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,国泰海通证券股份有限公司</t>
+          <t>长江证券股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
@@ -18703,7 +18705,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>广西绿城水务集团股份有限公司2026年度第四期中期票据</t>
+          <t>天津武清经济技术开发区有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18713,7 +18715,7 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2031-10-13</t>
+          <t>2029-04-12</t>
         </is>
       </c>
       <c r="AK79" s="3"/>
@@ -18724,7 +18726,7 @@
       </c>
       <c r="AM79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN79" s="3" t="inlineStr">
@@ -18744,22 +18746,22 @@
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18787,81 +18789,79 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ79" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ79" s="3"/>
     </row>
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26合产K5</t>
+          <t>26绿城水务MTN004</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>10-12 19:00</t>
+          <t>10-12 18:00</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>525033.SZ</t>
+          <t>102683910.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>7.5</v>
+        <v>3.0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 1.92</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>2.0</v>
+        <v>1.8</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>32.78</v>
+        <v>39.76</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26合产K3</t>
+          <t>26绿城水务MTN003</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>9.76Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>2.0005</t>
+          <t>1.9125</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>2.0300/--</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>合肥市产业投资控股(集团)有限公司</t>
+          <t>广西绿城水务集团股份有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C- 22.74</t>
+          <t>C- 14.31</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="S80" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr">
@@ -18885,44 +18885,44 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>5.8</v>
+        <v>4.65</v>
       </c>
       <c r="V80" s="3"/>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>2.16%~2.26%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金规模15亿元,募集资金扣除发行费用后,13亿元用于置换前期科技创新领域基金出资及股权直投,2亿元用于偿还银行贷款本息。</t>
+          <t>发行人拟发行金额为3亿元,用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司</t>
+          <t>兴业银行股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
       <c r="AE80" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF80" s="3" t="inlineStr">
@@ -18932,12 +18932,12 @@
       </c>
       <c r="AG80" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>合肥市产业投资控股(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
+          <t>广西绿城水务集团股份有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18947,86 +18947,88 @@
       </c>
       <c r="AJ80" s="3" t="inlineStr">
         <is>
-          <t>2036-10-13</t>
+          <t>2031-10-13</t>
         </is>
       </c>
       <c r="AK80" s="3"/>
       <c r="AL80" s="3" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AM80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AN80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AO80" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP80" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ80" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR80" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AS80" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AT80" s="3" t="inlineStr">
+        <is>
+          <t>水务</t>
+        </is>
+      </c>
+      <c r="AU80" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM80" s="3" t="inlineStr">
+      <c r="AV80" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW80" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX80" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY80" s="3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AN80" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AO80" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP80" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ80" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR80" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS80" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT80" s="3" t="inlineStr">
-        <is>
-          <t>塑料</t>
-        </is>
-      </c>
-      <c r="AU80" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV80" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW80" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX80" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY80" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AZ80" s="3"/>
+      <c r="AZ80" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26合产K4</t>
+          <t>26合产K5</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -19036,54 +19038,54 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>525032.SZ</t>
+          <t>525033.SZ</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
         <v>7.5</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1.47</v>
+        <v>2.0</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>19.26</v>
+        <v>32.78</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26合产K2</t>
+          <t>26合产K3</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>2.76Y</t>
+          <t>9.76Y</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1.6163</t>
+          <t>2.0005</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0300/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
@@ -19117,7 +19119,7 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="V81" s="3"/>
       <c r="W81" s="3" t="inlineStr">
@@ -19127,7 +19129,7 @@
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>2.16%~2.26%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -19169,7 +19171,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>合肥市产业投资控股(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>合肥市产业投资控股(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -19179,14 +19181,10 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2029-10-13</t>
-        </is>
-      </c>
-      <c r="AK81" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2036-10-13</t>
+        </is>
+      </c>
+      <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
           <t/>
@@ -19262,74 +19260,74 @@
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26鼓风机SCP002</t>
+          <t>26合产K4</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>10-12 18:00</t>
+          <t>10-12 19:00</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>012682405.IB</t>
+          <t>525032.SZ</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>19.46</v>
+        <v>19.26</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>26鼓风机MTN002(科创债)</t>
+          <t>26合产K2</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>2.32Y</t>
+          <t>2.76Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1.6765</t>
+          <t>1.6163</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>--/1.6200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>陕西鼓风机(集团)有限公司</t>
+          <t>合肥市产业投资控股(集团)有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.63</t>
+          <t>C- 22.74</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19339,12 +19337,12 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>10-12 10:00</t>
+          <t>10-12 15:00</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T82" s="3" t="inlineStr">
@@ -19353,46 +19351,44 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>2.13</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.60%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模5亿元,用途为偿还发行人本部到期债务融资工具[26鼓风机SCP001(科创债)]</t>
+          <t>本期债券募集资金规模15亿元,募集资金扣除发行费用后,13亿元用于置换前期科技创新领域基金出资及股权直投,2亿元用于偿还银行贷款本息。</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,交通银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF82" s="3" t="inlineStr">
@@ -19402,12 +19398,12 @@
       </c>
       <c r="AG82" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>陕西鼓风机(集团)有限公司2026年度第二期超短期融资券</t>
+          <t>合肥市产业投资控股(集团)有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -19417,7 +19413,7 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2027-07-10</t>
+          <t>2029-10-13</t>
         </is>
       </c>
       <c r="AK82" s="3" t="inlineStr">
@@ -19427,12 +19423,12 @@
       </c>
       <c r="AL82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t/>
         </is>
       </c>
       <c r="AM82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AN82" s="3" t="inlineStr">
@@ -19447,27 +19443,27 @@
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>其他通用设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>其他通用设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>塑料</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -19495,14 +19491,12 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ82" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ82" s="3"/>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26中建六局SCP001</t>
+          <t>26鼓风机SCP002</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -19512,7 +19506,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>012682409.IB</t>
+          <t>012682405.IB</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -19521,55 +19515,55 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.70</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>24.46</v>
+        <v>19.46</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>25中建六局MTN001(科创债)</t>
+          <t>26鼓风机MTN002(科创债)</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>8.78Y</t>
+          <t>2.32Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>2.2330</t>
+          <t>1.6765</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司</t>
+          <t>陕西鼓风机(集团)有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.30</t>
+          <t>B+ 59.63</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19579,12 +19573,12 @@
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>10-12 09:00</t>
+          <t>10-12 10:00</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="T83" s="3" t="inlineStr">
@@ -19593,40 +19587,40 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>4.43</v>
+        <v>2.94</v>
       </c>
       <c r="V83" s="4" t="n">
-        <v>1.2</v>
+        <v>2.13</v>
       </c>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.58%</t>
+          <t>1.56%~1.60%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z83" s="3"/>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额6亿元。本期超短期融资券全部募集资金拟用于偿还有息负债(流动资金贷款)</t>
+          <t>本期超短期融资券发行规模5亿元,用途为偿还发行人本部到期债务融资工具[26鼓风机SCP001(科创债)]</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,广发银行股份有限公司</t>
+          <t>兴业银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
@@ -19637,7 +19631,7 @@
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
@@ -19647,7 +19641,7 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第六工程局有限公司2026年度第一期超短期融资券</t>
+          <t>陕西鼓风机(集团)有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19657,10 +19651,14 @@
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="AK83" s="3"/>
+          <t>2027-07-10</t>
+        </is>
+      </c>
+      <c r="AK83" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL83" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -19683,27 +19681,27 @@
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>其他通用设备</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>其他通用设备</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
@@ -19731,12 +19729,14 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ83" s="3"/>
+      <c r="AZ83" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26中关租赁SCP002</t>
+          <t>26中建六局SCP001</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>012690004.IB</t>
+          <t>012682409.IB</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -19755,40 +19755,40 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.63</t>
+          <t>1.40 ~ 1.70</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>31.46</v>
+        <v>24.46</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>24中关租赁MTN001</t>
+          <t>25中建六局MTN001(科创债)</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>1.03Y</t>
+          <t>8.78Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.6498</t>
+          <t>2.2330</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -19798,12 +19798,12 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>中关村科技租赁股份有限公司</t>
+          <t>中国建筑第六工程局有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>D 4.89</t>
+          <t>B+ 59.30</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="S84" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T84" s="3" t="inlineStr">
@@ -19827,38 +19827,40 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V84" s="3"/>
+        <v>4.43</v>
+      </c>
+      <c r="V84" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.71%</t>
+          <t>1.54%~1.58%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z84" s="3"/>
       <c r="AA84" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模4亿元,募集资金拟用于偿还债务融资工具。[26中关租赁SCP001]</t>
+          <t>本期超短期融资券发行金额6亿元。本期超短期融资券全部募集资金拟用于偿还有息负债(流动资金贷款)</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,南京银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
@@ -19869,7 +19871,7 @@
       </c>
       <c r="AF84" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG84" s="3" t="inlineStr">
@@ -19879,7 +19881,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>中关村科技租赁股份有限公司2026年度第二期超短期融资券</t>
+          <t>中国建筑第六工程局有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19910,32 +19912,32 @@
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP84" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
@@ -19963,9 +19965,7 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ84" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ84" s="3"/>
     </row>
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-10-12.xlsx
+++ b/data/credit_bond_all_2026-10-12.xlsx
@@ -12458,7 +12458,7 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26皖投K3</t>
+          <t>26众安02</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12468,64 +12468,64 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>246168.SH</t>
+          <t>284052.SH</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>19.76</v>
+        <v>39.76</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>24皖投集MTN003</t>
+          <t>26众安01</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>4.65Y</t>
+          <t>2.77Y+2.00Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.7015</t>
+          <t>1.7957</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>江苏众安建设投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 20.91</t>
+          <t>C- 12.42</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>10-12 16:00</t>
+          <t>10-12 15:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -12549,41 +12549,45 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>6.08</v>
+        <v>3.75</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟全部用于偿还有息债务[25皖投集CP003]</t>
+          <t>本期债券募集资金不超过2.00亿元扣除发行费用后,拟全部用于偿还发行人到期的公司债券本金[21众安03]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国开证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD53" s="3"/>
+          <t>天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr">
+        <is>
+          <t>宿迁宿城国有资本控股(集团)有限公司</t>
+        </is>
+      </c>
       <c r="AE53" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12601,12 +12605,12 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>江苏众安建设投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ53" s="3" t="inlineStr">
@@ -12622,7 +12626,7 @@
       </c>
       <c r="AM53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AN53" s="3" t="inlineStr">
@@ -12632,47 +12636,47 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-14</t>
         </is>
       </c>
       <c r="AV53" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -12690,7 +12694,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26众安02</t>
+          <t>26株城07</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12700,64 +12704,64 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>284052.SH</t>
+          <t>283956.SH</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2.0</v>
+        <v>4.1</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2.0</v>
+        <v>4.1</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>39.76</v>
+        <v>47.76</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26众安01</t>
+          <t>26株洲城建PPN001</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2.77Y+2.00Y</t>
+          <t>4.69Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.7957</t>
+          <t>1.9006</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>江苏众安建设投资(集团)有限公司</t>
+          <t>株洲市城市建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C- 12.42</t>
+          <t>C+ 32.85</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12781,45 +12785,41 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>3.75</v>
+        <v>4.6098</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>湖南省-株洲市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过2.00亿元扣除发行费用后,拟全部用于偿还发行人到期的公司债券本金[21众安03]</t>
+          <t>本期债券发行规模为不超过人民币4.10亿元(含),募集资金扣除发行费用后,仅可用于偿还到期公司债券本金。[23株城08]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD54" s="3" t="inlineStr">
-        <is>
-          <t>宿迁宿城国有资本控股(集团)有限公司</t>
-        </is>
-      </c>
+          <t>财达证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>江苏众安建设投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>株洲市城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12868,47 +12868,47 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
         <is>
-          <t>2029-10-14</t>
+          <t/>
         </is>
       </c>
       <c r="AV54" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26株城07</t>
+          <t>26西投K4</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12936,64 +12936,64 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>283956.SH</t>
+          <t>284154.SH</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.1</v>
+        <v>3.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4.1</v>
+        <v>3.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>47.76</v>
+        <v>52.26</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26株洲城建PPN001</t>
+          <t>26西投K2</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>4.69Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.9006</t>
+          <t>1.8734</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司</t>
+          <t>西安投资控股有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.85</t>
+          <t>C- 14.85</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>10-12 15:00</t>
+          <t>10-12 16:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -13017,17 +13017,17 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>4.6098</v>
+        <v>4.47</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -13038,17 +13038,17 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>湖南省-株洲市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币4.10亿元(含),募集资金扣除发行费用后,仅可用于偿还到期公司债券本金。[23株城08]</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的股权投资和基金出资款,剩余部分用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>财达证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,国投证券股份有限公司,国金证券股份有限公司,联储证券股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>株洲市城市建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -13079,10 +13079,14 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2031-10-14</t>
-        </is>
-      </c>
-      <c r="AK55" s="3"/>
+          <t>2029-10-14</t>
+        </is>
+      </c>
+      <c r="AK55" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL55" s="3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
@@ -13090,7 +13094,7 @@
       </c>
       <c r="AM55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AN55" s="3" t="inlineStr">
@@ -13100,12 +13104,12 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
@@ -13115,17 +13119,17 @@
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
@@ -13158,7 +13162,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26西投K4</t>
+          <t>26浦土02</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -13168,64 +13172,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>284154.SH</t>
+          <t>246180.SH</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>3.0</v>
+        <v>12.6</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3.0</v>
+        <v>12.6</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>52.26</v>
+        <v>30.76</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26西投K2</t>
+          <t>26浦土01</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.8734</t>
+          <t>1.7066</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司</t>
+          <t>上海浦东土地控股(集团)有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 14.85</t>
+          <t>D+ 7.23</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13235,7 +13239,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>10-12 16:00</t>
+          <t>10-12 15:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -13249,38 +13253,38 @@
         </is>
       </c>
       <c r="U56" s="4" t="n">
-        <v>4.47</v>
+        <v>4.21</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>上海市-浦东新区</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不低于70%募集资金用于置换前12个月内科技创新领域的股权投资和基金出资款,剩余部分用于偿还有息债务。</t>
+          <t>本期债券发行金额为不超过12.60亿元(含12.60亿元)公司拟将本期债券募集资金扣除发行费用后全部用于偿还公司债券本金[23浦土02]</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,首创证券股份有限公司,开源证券股份有限公司,国投证券股份有限公司,国金证券股份有限公司,联储证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -13301,32 +13305,28 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>西安投资控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第三期)</t>
+          <t>上海浦东土地控股(集团)有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2029-10-14</t>
-        </is>
-      </c>
-      <c r="AK56" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-14</t>
+        </is>
+      </c>
+      <c r="AK56" s="3"/>
       <c r="AL56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
@@ -13336,32 +13336,32 @@
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13394,74 +13394,74 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26浦土02</t>
+          <t>26中关租赁SCP002</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>10-12 19:00</t>
+          <t>10-12 18:00</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>246180.SH</t>
+          <t>012690004.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>12.6</v>
+        <v>4.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>12.6</v>
+        <v>4.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 1.63</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>30.76</v>
+        <v>31.46</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26浦土01</t>
+          <t>24中关租赁MTN001</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>1.03Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.7066</t>
+          <t>1.6498</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>1.7800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>上海浦东土地控股(集团)有限公司</t>
+          <t>中关村科技租赁股份有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.23</t>
+          <t>D 4.89</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13471,58 +13471,58 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>10-12 15:00</t>
+          <t>10-12 09:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>4.21</v>
+        <v>2.5</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.67%~1.71%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>上海市-浦东新区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过12.60亿元(含12.60亿元)公司拟将本期债券募集资金扣除发行费用后全部用于偿还公司债券本金[23浦土02]</t>
+          <t>发行人本期超短期融资券发行规模4亿元,募集资金拟用于偿还债务融资工具。[26中关租赁SCP001]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>北京银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>上海浦东土地控股(集团)有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>中关村科技租赁股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13547,60 +13547,60 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2031-10-14</t>
+          <t>2027-07-09</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
       <c r="AL57" s="3" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM57" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="AO57" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ57" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR57" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS57" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU57" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV57" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -13621,79 +13621,81 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AZ57" s="3"/>
+      <c r="AZ57" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26中关租赁SCP002</t>
+          <t>26浦口城乡MTN002</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>10-12 18:00</t>
+          <t>10-13 18:00</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>012690004.IB</t>
+          <t>102683937.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>4.0</v>
+        <v>2.74</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>4.0</v>
+        <v>2.74</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.63</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>31.46</v>
+        <v>42.52</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>24中关租赁MTN001</t>
+          <t>26浦口城乡MTN001</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>1.03Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.6498</t>
+          <t>1.7285</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>中关村科技租赁股份有限公司</t>
+          <t>南京浦口城乡建设集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>D 4.89</t>
+          <t>C- 10.58</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13708,26 +13710,24 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V58" s="3"/>
-      <c r="W58" s="3" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
+        <v>4.7518</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W58" s="3"/>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.71%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -13738,23 +13738,23 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模4亿元,募集资金拟用于偿还债务融资工具。[26中关租赁SCP001]</t>
+          <t xml:space="preserve">本期债务融资工具发行拟募集资金【2.74】亿元，所募集资金拟用于偿还发行人债务融资工具【23浦口城乡MTN003 】。 </t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,南京银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>中关村科技租赁股份有限公司2026年度第二期超短期融资券</t>
+          <t>南京浦口城乡建设集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13779,155 +13779,157 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2027-07-09</t>
-        </is>
-      </c>
-      <c r="AK58" s="3"/>
+          <t>2029-10-14</t>
+        </is>
+      </c>
+      <c r="AK58" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL58" s="3" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="AM58" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="AN58" s="3" t="inlineStr">
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY58" s="3" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AO58" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ58" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR58" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS58" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT58" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU58" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV58" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW58" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX58" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY58" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AZ58" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ58" s="3"/>
     </row>
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26浦口城乡MTN002</t>
+          <t>26皖投K3</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>10-13 18:00</t>
+          <t>10-12 19:00</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>102683937.IB</t>
+          <t>246168.SH</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2.74</v>
+        <v>5.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2.74</v>
+        <v>4.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>42.52</v>
+        <v>19.76</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26浦口城乡MTN001</t>
+          <t>24皖投集MTN003</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>4.65Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.7285</t>
+          <t>1.7015</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>南京浦口城乡建设集团有限公司</t>
+          <t>安徽省投资集团控股有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 10.58</t>
+          <t>C- 20.91</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13937,12 +13939,12 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>10-12 09:00</t>
+          <t>10-12 16:00</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
@@ -13951,42 +13953,44 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>4.7518</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W59" s="3"/>
+        <v>6.08</v>
+      </c>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债务融资工具发行拟募集资金【2.74】亿元，所募集资金拟用于偿还发行人债务融资工具【23浦口城乡MTN003 】。 </t>
+          <t>本期债券拟全部用于偿还有息债务[25皖投集CP003]</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国信证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
@@ -13996,12 +14000,12 @@
       </c>
       <c r="AG59" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>南京浦口城乡建设集团有限公司2026年度第二期中期票据</t>
+          <t>安徽省投资集团控股有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -14011,22 +14015,18 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2029-10-14</t>
-        </is>
-      </c>
-      <c r="AK59" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-10-14</t>
+        </is>
+      </c>
+      <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AM59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AN59" s="3" t="inlineStr">
@@ -14036,32 +14036,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="AY59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AZ59" s="3"/>
